--- a/tools/config-xlsx/craft.xlsx
+++ b/tools/config-xlsx/craft.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:E4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,12 +416,6 @@
       <c r="E1" t="str">
         <v>costForgeStone</v>
       </c>
-      <c r="F1" t="str">
-        <v>costGemShard</v>
-      </c>
-      <c r="G1" t="str">
-        <v>costRuneDust</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -439,12 +433,6 @@
       <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -460,13 +448,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>20</v>
-      </c>
-      <c r="F3">
-        <v>3</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -483,18 +465,12 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>6</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/tools/config-xlsx/craft.xlsx
+++ b/tools/config-xlsx/craft.xlsx
@@ -431,7 +431,7 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -448,7 +448,7 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>25</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
@@ -465,7 +465,7 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
